--- a/out-drill-b/out-drafted/a1/a1.xlsx
+++ b/out-drill-b/out-drafted/a1/a1.xlsx
@@ -12,13 +12,15 @@
     <sheet name="Issues" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Stages" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Assumptions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Date coverage" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'A1 register'!$A$4:$Y$206</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dates'!$A$1:$H$133</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Issues'!$A$1:$E$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Stages'!$A$1:$K$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Issues'!$A$1:$E$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Stages'!$A$1:$J$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Assumptions'!$A$1:$D$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Date coverage'!$A$1:$E$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -517,14 +519,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>A1 Obligations and compliance register — SLICE (Stage 2 first connected version)</t>
+          <t>A1 Obligations and compliance register — WORKING DRAFT</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>DRAFT. 202 representative rows, not the full register. Interpretations and amendment ops are PROPOSED by the assistant and not reviewed by a person; image readings are PENDING the owner's review. Validated state: ADD-02; working state ADD-03 is PARTIAL.</t>
+          <t>WORKING DRAFT, full register: 202 rows (review status: proposed 202; amendment ops: proposed 43). Rows and ops count as accepted only with a named person's decision bound to their current content. Image readings pending the owner's review: VOL-II-p3-r1, VOL-IV-p6-r1. Validated state: ADD-02; working state ADD-03 is PARTIAL.</t>
         </is>
       </c>
     </row>
@@ -768,7 +770,7 @@
       </c>
       <c r="W5" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-01/2.1: proposed</t>
         </is>
       </c>
       <c r="X5" s="4" t="inlineStr">
@@ -1740,7 +1742,7 @@
       </c>
       <c r="W13" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-01/4.1: proposed; ADD-02/9.1: proposed</t>
         </is>
       </c>
       <c r="X13" s="4" t="inlineStr">
@@ -2228,7 +2230,7 @@
       </c>
       <c r="W17" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-01/AppA/para1: proposed</t>
         </is>
       </c>
       <c r="X17" s="4" t="inlineStr">
@@ -2839,7 +2841,7 @@
       </c>
       <c r="W22" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-02/7.1: proposed</t>
         </is>
       </c>
       <c r="X22" s="4" t="inlineStr">
@@ -2958,7 +2960,7 @@
       </c>
       <c r="W23" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-02/4.1: proposed</t>
         </is>
       </c>
       <c r="X23" s="4" t="inlineStr">
@@ -3184,7 +3186,7 @@
       </c>
       <c r="W25" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-02/T1-1-rev/note(2): proposed</t>
         </is>
       </c>
       <c r="X25" s="4" t="inlineStr">
@@ -3529,7 +3531,7 @@
       </c>
       <c r="W28" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-02/3.1: proposed</t>
         </is>
       </c>
       <c r="X28" s="4" t="inlineStr">
@@ -3644,7 +3646,7 @@
       </c>
       <c r="W29" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-02/3.1: proposed</t>
         </is>
       </c>
       <c r="X29" s="4" t="inlineStr">
@@ -3759,7 +3761,7 @@
       </c>
       <c r="W30" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-02/5.1: proposed</t>
         </is>
       </c>
       <c r="X30" s="4" t="inlineStr">
@@ -4354,7 +4356,7 @@
       </c>
       <c r="W35" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-02/7.1: proposed</t>
         </is>
       </c>
       <c r="X35" s="4" t="inlineStr">
@@ -4473,7 +4475,7 @@
       </c>
       <c r="W36" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-02/7.1: proposed</t>
         </is>
       </c>
       <c r="X36" s="4" t="inlineStr">
@@ -4592,7 +4594,7 @@
       </c>
       <c r="W37" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-02/7.1: proposed</t>
         </is>
       </c>
       <c r="X37" s="4" t="inlineStr">
@@ -7607,7 +7609,7 @@
       </c>
       <c r="W62" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-02/2.1: proposed</t>
         </is>
       </c>
       <c r="X62" s="4" t="inlineStr">
@@ -9162,7 +9164,7 @@
       </c>
       <c r="W75" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-02/3.1: proposed</t>
         </is>
       </c>
       <c r="X75" s="4" t="inlineStr">
@@ -9277,7 +9279,7 @@
       </c>
       <c r="W76" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-02/3.1: proposed</t>
         </is>
       </c>
       <c r="X76" s="4" t="inlineStr">
@@ -9392,7 +9394,7 @@
       </c>
       <c r="W77" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-02/3.1: proposed</t>
         </is>
       </c>
       <c r="X77" s="4" t="inlineStr">
@@ -9507,7 +9509,7 @@
       </c>
       <c r="W78" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-02/3.1: proposed</t>
         </is>
       </c>
       <c r="X78" s="4" t="inlineStr">
@@ -14441,7 +14443,7 @@
       </c>
       <c r="W120" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-02/4.1: proposed</t>
         </is>
       </c>
       <c r="X120" s="4" t="inlineStr">
@@ -15028,7 +15030,7 @@
       </c>
       <c r="W125" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-01/5.1: proposed</t>
         </is>
       </c>
       <c r="X125" s="4" t="inlineStr">
@@ -15143,7 +15145,7 @@
       </c>
       <c r="W126" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-01/5.1: proposed</t>
         </is>
       </c>
       <c r="X126" s="4" t="inlineStr">
@@ -18661,7 +18663,7 @@
       </c>
       <c r="W156" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-01/AppA/para1: proposed</t>
         </is>
       </c>
       <c r="X156" s="4" t="inlineStr">
@@ -18780,7 +18782,7 @@
       </c>
       <c r="W157" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-01/AppA/para1: proposed</t>
         </is>
       </c>
       <c r="X157" s="4" t="inlineStr">
@@ -18903,7 +18905,7 @@
       </c>
       <c r="W158" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-01/AppA/para1: proposed</t>
         </is>
       </c>
       <c r="X158" s="4" t="inlineStr">
@@ -19022,7 +19024,7 @@
       </c>
       <c r="W159" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-01/AppA/para1: proposed</t>
         </is>
       </c>
       <c r="X159" s="4" t="inlineStr">
@@ -19141,7 +19143,7 @@
       </c>
       <c r="W160" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-01/AppA/para1: proposed</t>
         </is>
       </c>
       <c r="X160" s="4" t="inlineStr">
@@ -19260,7 +19262,7 @@
       </c>
       <c r="W161" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-01/AppA/para1: proposed</t>
         </is>
       </c>
       <c r="X161" s="4" t="inlineStr">
@@ -23785,7 +23787,7 @@
       </c>
       <c r="W200" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-02/8.1: proposed</t>
         </is>
       </c>
       <c r="X200" s="4" t="inlineStr">
@@ -29792,7 +29794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -30683,12 +30685,12 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-STALE</t>
+          <t>I-AUTO-UNTRACED-ADD-03</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>3 row(s) STALE at ADD-02: a dependency changed after the interpretation was made (dates recomputed; the reading needs a person). Rows: VOL-I-8.3-01, VOL-I-3.4-01, VOL-I-6.7-01</t>
+          <t>ADD-03: obligation(s) not carried through to the outputs (C46): ADD-03/cover/para3 [A1] 'This Addendum amends Volume I Clauses 5.2, 6.7 and 7.1, adds Volume I Clause 4.4 and a requirement for certifi'. A row, its consequence or its deliverable is missing; a person must add it</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -30698,24 +30700,20 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>C11 (automatic)</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>VOL-I-8.3-01; VOL-I-3.4-01; VOL-I-6.7-01</t>
-        </is>
-      </c>
+          <t>C46 (automatic)</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-COUNTING</t>
+          <t>I-AUTO-STALE</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Counting conventions not stated in the pack for ATTENDANCE-NOTICE, BID-BOND-VALIDITY, PROPOSAL-VALIDITY, PROPOSAL-VALIDITY-F4A, REFERENCE-LOOKBACK: every reading is shown (A1 Dates); planning uses the conservative reading (config/assumptions.yaml)</t>
+          <t>3 row(s) STALE at ADD-02: a dependency changed after the interpretation was made (dates recomputed; the reading needs a person). Rows: VOL-I-8.3-01, VOL-I-3.4-01, VOL-I-6.7-01</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -30725,79 +30723,79 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>D4 (automatic)</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr"/>
+          <t>C11 (automatic)</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-8.3-01; VOL-I-3.4-01; VOL-I-6.7-01</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-PENDING-READINGS</t>
+          <t>I-AUTO-COUNTING</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>20 row(s) rely on image readings (Table 2-4, Form 4-C) still pending the owner's review. Rows: VOL-I-9.4-01, VOL-II-2.5-01, VOL-II-T2-4-BOD5, VOL-II-T2-4-COD, VOL-II-T2-4-FaecalColiforms, VOL-II-T2-4-NOTE1, VOL-II-T2-4-OilGrease, VOL-II-T2-4-ResidualChlorine, VOL-II-T2-4-TN, VOL-II-T2-4-TP, VOL-II-T2-4-TSS, VOL-II-T2-4-Turbidity, VOL-II-T2-4-pH, VOL-IV-F4C-01, VOL-IV-F4C-02, VOL-IV-F4C-03, VOL-IV-F4C-04, VOL-IV-F4C-05, VOL-IV-F4C-N1, VOL-V-29.3-01</t>
+          <t>Counting conventions not stated in the pack for ATTENDANCE-NOTICE, BID-BOND-VALIDITY, PROPOSAL-VALIDITY, PROPOSAL-VALIDITY-F4A, REFERENCE-LOOKBACK: every reading is shown (A1 Dates); planning uses the conservative reading (config/assumptions.yaml)</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Bid manager</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>readings (automatic)</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>VOL-I-9.4-01; VOL-II-2.5-01; VOL-II-T2-4-BOD5; VOL-II-T2-4-COD; VOL-II-T2-4-FaecalColiforms; VOL-II-T2-4-NOTE1; VOL-II-T2-4-OilGrease; VOL-II-T2-4-ResidualChlorine; VOL-II-T2-4-TN; VOL-II-T2-4-TP; VOL-II-T2-4-TSS; VOL-II-T2-4-Turbidity; VOL-II-T2-4-pH; VOL-IV-F4C-01; VOL-IV-F4C-02; VOL-IV-F4C-03; VOL-IV-F4C-04; VOL-IV-F4C-05; VOL-IV-F4C-N1; VOL-V-29.3-01</t>
-        </is>
-      </c>
+          <t>D4 (automatic)</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>I-A5-lcc-ratio</t>
+          <t>I-AUTO-PENDING-READINGS</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>A5 lcc-ratio: INFEASIBLE by 12 WD (latest start 2026-10-06 is before the status date 2026-10-22; not compressed) (VOL-I-8.6-01; duration 5 WD is an ASSUMPTION: lcc_ratio_calc)</t>
+          <t>20 row(s) rely on image readings (Table 2-4, Form 4-C) still pending the owner's review. Rows: VOL-I-9.4-01, VOL-II-2.5-01, VOL-II-T2-4-BOD5, VOL-II-T2-4-COD, VOL-II-T2-4-FaecalColiforms, VOL-II-T2-4-NOTE1, VOL-II-T2-4-OilGrease, VOL-II-T2-4-ResidualChlorine, VOL-II-T2-4-TN, VOL-II-T2-4-TP, VOL-II-T2-4-TSS, VOL-II-T2-4-Turbidity, VOL-II-T2-4-pH, VOL-IV-F4C-01, VOL-IV-F4C-02, VOL-IV-F4C-03, VOL-IV-F4C-04, VOL-IV-F4C-05, VOL-IV-F4C-N1, VOL-V-29.3-01</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>A5 (automatic)</t>
+          <t>readings (automatic)</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-8.6-01</t>
+          <t>VOL-I-9.4-01; VOL-II-2.5-01; VOL-II-T2-4-BOD5; VOL-II-T2-4-COD; VOL-II-T2-4-FaecalColiforms; VOL-II-T2-4-NOTE1; VOL-II-T2-4-OilGrease; VOL-II-T2-4-ResidualChlorine; VOL-II-T2-4-TN; VOL-II-T2-4-TP; VOL-II-T2-4-TSS; VOL-II-T2-4-Turbidity; VOL-II-T2-4-pH; VOL-IV-F4C-01; VOL-IV-F4C-02; VOL-IV-F4C-03; VOL-IV-F4C-04; VOL-IV-F4C-05; VOL-IV-F4C-N1; VOL-V-29.3-01</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>I-A5-attendance-notice</t>
+          <t>I-A5-lcc-ratio</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>A5 attendance-notice: DEADLINE PASSED (ATTENDANCE-NOTICE = 2026-10-14 is before the status date 2026-10-22; record whether it was done) (ADD-01-3.1-01, VOL-I-5.4-01; duration 2 WD is an ASSUMPTION: clarification_drafting)</t>
+          <t>A5 lcc-ratio: INFEASIBLE by 12 WD (latest start 2026-10-06 is before the status date 2026-10-22; not compressed) (VOL-I-8.6-01; duration 5 WD is an ASSUMPTION: lcc_ratio_calc)</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Bid management</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -30807,24 +30805,24 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>ADD-01-3.1-01; VOL-I-5.4-01</t>
+          <t>VOL-I-8.6-01</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>I-A5-lcc-certificate</t>
+          <t>I-A5-attendance-notice</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>A5 lcc-certificate: INFEASIBLE by 7 WD (latest start 2026-10-13 is before the status date 2026-10-22; not compressed) (VOL-I-8.6-01; duration 30 WD is an ASSUMPTION: lcc_certificate)</t>
+          <t>A5 attendance-notice: DEADLINE PASSED (ATTENDANCE-NOTICE = 2026-10-14 is before the status date 2026-10-22; record whether it was done) (ADD-01-3.1-01, VOL-I-5.4-01; duration 2 WD is an ASSUMPTION: clarification_drafting)</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Bid management</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -30834,39 +30832,66 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-8.6-01</t>
+          <t>ADD-01-3.1-01; VOL-I-5.4-01</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
+          <t>I-A5-lcc-certificate</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>A5 lcc-certificate: INFEASIBLE by 7 WD (latest start 2026-10-13 is before the status date 2026-10-22; not compressed) (VOL-I-8.6-01; duration 30 WD is an ASSUMPTION: lcc_certificate)</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>A5 (automatic)</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-8.6-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
           <t>I-A5-FEASIBILITY</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>A5 at the status date: lcc-ratio INFEASIBLE by 12 WD; attendance-notice DEADLINE PASSED; lcc-certificate INFEASIBLE by 7 WD. Lead times are PROVISIONAL assumptions (A5 drivers)</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>Bid manager</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D42" s="4" t="inlineStr">
         <is>
           <t>A5 (automatic)</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
+      <c r="E42" s="4" t="inlineStr">
         <is>
           <t>ADD-01-3.1-01; VOL-I-5.4-01; VOL-I-8.6-01</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E41"/>
+  <autoFilter ref="A1:E42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -30877,7 +30902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -30886,11 +30911,10 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30936,15 +30960,10 @@
       </c>
       <c r="I1" s="3" t="inlineStr">
         <is>
-          <t>Outside slice</t>
+          <t>Unresolved</t>
         </is>
       </c>
       <c r="J1" s="3" t="inlineStr">
-        <is>
-          <t>Unresolved</t>
-        </is>
-      </c>
-      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>Validated</t>
         </is>
@@ -30976,10 +30995,7 @@
       <c r="I2" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="4" t="b">
+      <c r="J2" s="4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -31012,7 +31028,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>proposed 15</t>
         </is>
       </c>
       <c r="H3" s="4" t="n">
@@ -31021,10 +31037,7 @@
       <c r="I3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="4" t="b">
+      <c r="J3" s="4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -31057,7 +31070,7 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>proposed 22</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
@@ -31066,10 +31079,7 @@
       <c r="I4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="4" t="b">
+      <c r="J4" s="4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -31102,24 +31112,21 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>proposed 6</t>
         </is>
       </c>
       <c r="H5" s="4" t="n">
         <v>11</v>
       </c>
       <c r="I5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J5" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K5" s="4" t="b">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K5"/>
+  <autoFilter ref="A1:J5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -32507,4 +32514,1295 @@
   <autoFilter ref="A1:D62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="80" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Phrase</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Treatment</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>By</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Sentence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:cover/para3</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>disposition</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>informational: tender reference and date of issue (14 September 2026, the start of the VOL-I 4.2 blackout)</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:4.3</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>two (2) Working Days</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-4.3-01 SPOC-CHANGE-NOTICE</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Each Bidder shall nominate a single point of contact and shall notify the Authority of any change within two (2) Working Days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:5.2</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>ten (10) Working Days</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-5.2-01 CLARIFICATION-CUTOFF</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Requests for clarification shall be submitted no later than ten (10) Working Days before the Proposal Due Date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:5.4</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-5.4-01 PRE-BID</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>A Pre-Bid Conference will be held on Wednesday 30 September 2026 at 10:00 Riyadh time at the Authority's offices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:6.1</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>00 hours</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-6.1-01 PDD</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Proposals shall be received by the Authority not later than 14:00 hours Riyadh time on Thursday 26 November 2026 at the address given in Appendix 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:6.1</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>26 November 2026</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>anchor</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>defines PDD</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Proposals shall be received by the Authority not later than 14:00 hours Riyadh time on Thursday 26 November 2026 at the address given in Appendix 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:6.3</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>eighty (180) days</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-6.3-01 BID-BOND-VALIDITY</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Envelope A shall be accompanied by a Bid Bond which shall remain valid for one hundred and eighty (180) days from the Proposal Due Date and shall be extended on demand where the Authority extends the period of Proposal v</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:7.1</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>fifty (150) days</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-7.1-01 PROPOSAL-VALIDITY</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Each Proposal shall remain open for acceptance for one hundred and fifty (150) days from the Proposal Due Date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:8.5#fn12</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>ten (10) years</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-8.5-01 REFERENCE-LOOKBACK</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>For the avoidance of doubt, a Bidder that does not evidence at least two (2) reference sewage treatment plants, each of nominal capacity not less than 80,000 m³/day and each having achieved commercial operation within th</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:8.8</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>five (5) years</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>duration</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-8.8-01 quotes it as part of the requirement</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>The proposed O&amp;M Operator shall evidence not less than five (5) years of continuous operation of at least one (1) wastewater treatment facility of nominal capacity not less than 50,000 m³/day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:8.10</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>five (5) years</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-8.10-01 DEBARMENT-LOOKBACK</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>No member of the Bidder shall be the subject of, or have been the subject of within the preceding five (5) years, any debarment by a public authority in the Kingdom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:12.1</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>twenty-five (25) years</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-12.1-01 CONCESSION-END-PCOD</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>The concession period shall be twenty-five (25) years commencing on the Project Commercial Operation Date, following which the Project shall transfer to the Authority in accordance with Volume V.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:12.2</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>twenty (120) days</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-12.2-01 PB-COMMERCIAL-CLOSE</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>The Preferred Bidder shall achieve Commercial Close within one hundred and twenty (120) days, and Financial Close within two hundred and seventy (270) days, of the date of the Preferred Bidder Notification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:12.2</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>seventy (270) days</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-12.2-02 PB-FINANCIAL-CLOSE</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>The Preferred Bidder shall achieve Commercial Close within one hundred and twenty (120) days, and Financial Close within two hundred and seventy (270) days, of the date of the Preferred Bidder Notification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:12.3</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>ten (10) Working Days</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>disposition</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>authority: standstill of ten Working Days before the Authority executes the Project Agreement; no bidder action</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>A standstill period of ten (10) Working Days shall apply between the Preferred Bidder Notification and execution of the Project Agreement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:12.4</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>twenty (20) Working Days</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>disposition</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>informational: an optional right of unsuccessful Bidders to request a debrief; not an obligation</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Unsuccessful Bidders may request a debrief within twenty (20) Working Days of notification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:cover/para3</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>disposition</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>informational: tender reference and date of issue (14 September 2026, fixed)</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:2.2</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>fifty (50) years</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>duration</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II-2.2-01 quotes it as part of the requirement</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>The design life of all civil structures shall be not less than fifty (50) years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:2.2</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>twenty (20) years</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>duration</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II-2.2-02 quotes it as part of the requirement</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>The design life of mechanical and electrical equipment shall be not less than twenty (20) years or the manufacturer's rated life, whichever is the shorter, with lifecycle replacement provided for in the Project Company's</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:3.2</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>seven (7) years</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>duration</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II-3.2-02 quotes it as part of the requirement</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Where a membrane process is proposed, the Project Company shall demonstrate membrane replacement provisions in the lifecycle plan and shall warrant a membrane life of not less than seven (7) years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:4.4</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>ninety-six (96) hours</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>duration</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II-4.4-01 quotes it as part of the requirement</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Standby power shall be sized to carry the full inlet works, the disinfection stage and the effluent pumping station for not less than ninety-six (96) hours.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:5.5</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>475 years</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>duration</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II-5.5-01 quotes it as part of the requirement</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>All permanent civil structures shall be designed for a seismic event with a return period of 475 years and for a flood with a return period of 100 years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:5.5</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>100 years</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>duration</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II-5.5-02 quotes it as part of the requirement</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>All permanent civil structures shall be designed for a seismic event with a return period of 475 years and for a flood with a return period of 100 years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:6.4</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>seven (7) years</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>duration</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II-6.4-01 quotes it as part of the requirement</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>All process data shall be retained for not less than seven (7) years and shall be made available to the Authority on demand in a non-proprietary format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:7.2</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>thirty (30) days</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>duration</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II-7.2-01 quotes it as part of the requirement</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>PCOD shall not be certified until the Facility has completed a continuous reliability run of thirty (30) days at not less than 90% of nominal capacity, during which every parameter in Table 2-4 has been met.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:7.4</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>sixty (60) days</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II-7.4-01 VOL-II-AS-BUILT-DUE</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>The Project Company shall provide as-built documentation, operation and maintenance manuals, and an asset register in the Authority's standard format not later than sixty (60) days after PCOD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:8.1</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>two (2) years</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>duration</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II-8.1-01 quotes it as part of the requirement</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>The Project Company shall hold a spare parts inventory sufficient for two (2) years of normal operation for all items with a lead time exceeding twelve (12) weeks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:8.1</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>twelve (12) weeks</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>duration</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II-8.1-01 quotes it as part of the requirement</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>The Project Company shall hold a spare parts inventory sufficient for two (2) years of normal operation for all items with a lead time exceeding twelve (12) weeks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:8.5</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>two (2) years</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II-8.5-01 VOL-II-HANDBACK-SURVEY-WINDOW</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>A handback condition survey shall be carried out in the final two (2) years of the concession, and any remedial works identified shall be completed before transfer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>VOL-IV:cover/para3</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>disposition</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>informational: tender reference and issue date (14 September 2026, a fixed date); no bidder obligation</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:cover/para3</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>disposition</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>informational: tender reference and date of issue (14 September 2026, fixed)</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:3.1</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>twenty-five (25) years</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-3.1-01 VOL-V-TERM-END</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>This Agreement shall come into force on the Effective Date and shall continue for a period of twenty-five (25) years from the Effective Date, unless terminated earlier in accordance with its terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:12.1</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>thirty-six (36) months</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-12.1-01 VOL-V-SCHEDULED-PCOD</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>The Project Company shall achieve PCOD within thirty-six (36) months of the Notice to Proceed (the Scheduled PCOD).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:18.3</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>sixty-five (365) days</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-18.3-01 VOL-V-PCOD-LONG-STOP</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>If PCOD has not been achieved within three hundred and sixty-five (365) days after the Scheduled PCOD, the Authority may terminate under Clause 39.2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:29.3</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>twelve (12) months</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-29.3-01 VOL-V-RAMP-UP-END</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>During the first twelve (12) months after PCOD (the Ramp-Up Period) the Availability Payment shall be paid at ninety per cent (90%) of the full rate, and no availability deduction shall apply to a parameter listed in Tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:29.4</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>ten (10) Working Days</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-29.4-01 VOL-V-INVOICE-DUE</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Invoices shall be submitted within ten (10) Working Days of each month end and shall be paid within thirty (30) days of receipt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:29.4</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>thirty (30) days</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-29.4-01 VOL-V-INVOICE-DUE</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Invoices shall be submitted within ten (10) Working Days of each month end and shall be paid within thirty (30) days of receipt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:31.3</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>twenty-four (24) hours</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>duration</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-31.3-02 quotes it as part of the requirement</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>A cure period of twenty-four (24) hours applies to an Unavailability Event under Clause 31.1(a) and of seventy-two (72) hours to an event under Clause 31.1(c).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:31.3</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>seventy-two (72) hours</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>duration</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-31.3-01 quotes it as part of the requirement</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>A cure period of twenty-four (24) hours applies to an Unavailability Event under Clause 31.1(a) and of seventy-two (72) hours to an event under Clause 31.1(c).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:31.4</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>ninety (90) day</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>duration</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-31.4-01 quotes it as part of the requirement</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>Persistent breach, being three (3) or more Unavailability Events in any rolling ninety (90) day period, entitles the Authority to require a remediation plan and, on a second occurrence, to terminate under Clause 39.3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:34.3</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>five (5) Working Days</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-34.3-01 VOL-V-RELIEF-EVENT-NOTICE</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>The Project Company shall notify a Relief Event within five (5) Working Days of becoming aware of it, failing which no relief shall be granted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:39.4</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>sixty (60) days</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>disposition</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">informational: the Project Company's right to terminate for an Authority Event of Default (unpaid undisputed sum over SAR 20,000,000 for 60 days after notice); </t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>The Project Company may terminate for an Authority Event of Default, being a failure to pay an undisputed sum exceeding SAR 20,000,000 that continues for sixty (60) days after notice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:42.1</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>five (5) years</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>duration</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-42.1-02 quotes it as part of the requirement</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>The Project Company shall transfer the Facility to the Authority on expiry in the condition required by Volume II Clause 8.5, free of encumbrance and with a remaining design life of not less than five (5) years for all m</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>ADD-01:3.1</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>five (5) Working Days</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>ADD-01-3.1-01 ATTENDANCE-NOTICE</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>A Bidder that considers its attendance to have been incorrectly recorded shall notify the Authority through the Portal within five (5) Working Days of this Addendum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>ADD-01:AppA/proposal-due-date</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>12 November 2026</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>printed</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>prints the PDD as 2026-11-12; the effective date is 2026-11-26 (raised as an issue, C31; not corrected)</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>12 November 2026, 14:00 Riyadh time</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>ADD-02:F4-G/T1/4</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>twenty-four (24) hours</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>post_award</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>ADD-02-F4G-01: undertaking 4: notify security incidents within 24 hours of detection, after award; an event-driven period, not a bid-stage date</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Security incidents affecting the Facility will be notified to the Authority within twenty-four (24) hours of detection.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E47"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/out-drill-b/out-drafted/a1/a1.xlsx
+++ b/out-drill-b/out-drafted/a1/a1.xlsx
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'A1 register'!$A$4:$Y$206</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dates'!$A$1:$H$133</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Issues'!$A$1:$E$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Issues'!$A$1:$E$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Stages'!$A$1:$J$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Assumptions'!$A$1:$D$62</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Date coverage'!$A$1:$E$47</definedName>
@@ -29794,7 +29794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -30708,12 +30708,12 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-STALE</t>
+          <t>I-AUTO-SUMMARY-ADD-01</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>3 row(s) STALE at ADD-02: a dependency changed after the interpretation was made (dates recomputed; the reading needs a person). Rows: VOL-I-8.3-01, VOL-I-3.4-01, VOL-I-6.7-01</t>
+          <t>ADD-01's cover summary does not match its provisions (C28): [understated] 'responds to clarification requests 1 to 6', but ADD-01/Q4 adds an obligation (ADD-01:Q4): 'The geotechnical report in the data room is provided for information. Bidders shall satisfy themselves as to ground conditions.'; [omitted] ADD-01/3.1 adds an obligation (ADD-01:3.1); the summary does not mention it: 'The attendance record is held by the Authority. A Bidder that considers its attendance to have been incorrectly recorded shall notify the Authority through the Portal within five (5) Working Days of this Addendum.'; [omitted] ADD-01/AppA/para1 replaces VOL-IV:F4-A; the summary does not mention it: 'Form 4-A is reissued below to add the acknowledgement of Addenda at paragraph 1. Bidders shall use this version.'. The summary is never applied; a person decides whether to raise a clarification</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -30723,24 +30723,20 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>C11 (automatic)</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>VOL-I-8.3-01; VOL-I-3.4-01; VOL-I-6.7-01</t>
-        </is>
-      </c>
+          <t>C28 (automatic)</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-COUNTING</t>
+          <t>I-AUTO-SUMMARY-ADD-02</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Counting conventions not stated in the pack for ATTENDANCE-NOTICE, BID-BOND-VALIDITY, PROPOSAL-VALIDITY, PROPOSAL-VALIDITY-F4A, REFERENCE-LOOKBACK: every reading is shown (A1 Dates); planning uses the conservative reading (config/assumptions.yaml)</t>
+          <t>ADD-02's cover summary does not match its provisions (C28): [consequence not mentioned] ADD-02:7.2 states 'Failure to submit Form 4-G shall render the Proposal non-responsive.'; the summary says only 'adds Form 4-G'; [understated] 'reinstates Volume I Clause 8.6', but ADD-02/9.1 reinstates it in an amended form: 'The Bidder shall submit a Local Content Certificate issued by the competent authority evidencing a local content ratio of not less than thirty-five per cent (35%) for the construction phase. Failure …' (as issued: 'The Bidder shall submit a Local Content Certificate issued by the competent authority evidencing a local content ratio of not less than thirty per cent (30%) f…'); [consequence not mentioned] ADD-02:9.1 states 'Failure to submit the certificate shall render the Proposal non-responsive.'; the summary says only 'reinstates Volume I Clause 8.6'; [omitted] ADD-02/T1-1-rev/note(2) amends VOL-I:11.2; the summary does not mention it: '(2) The combined score weighting stated in Volume I Clause 11.2 is amended to sixty-five per cent (65%) technical and thirty-five per cent (35%) commercial.'; [omitted] ADD-02/5.2 adds an obligation (VOL-II:S3); the summary does not mention it: 'Bidders shall reflect the amended limit in the process design submitted under Volume II Section 3.'; [omitted] ADD-02/9.2 ends the effect of ADD-01:4.2; the summary does not mention it: 'Section 4.2 of Addendum No. 1 ceases to have effect.'. The summary is never applied; a person decides whether to raise a clarification</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -30750,7 +30746,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>D4 (automatic)</t>
+          <t>C28 (automatic)</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr"/>
@@ -30758,140 +30754,213 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-PENDING-READINGS</t>
+          <t>I-AUTO-SUMMARY-ADD-03</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>20 row(s) rely on image readings (Table 2-4, Form 4-C) still pending the owner's review. Rows: VOL-I-9.4-01, VOL-II-2.5-01, VOL-II-T2-4-BOD5, VOL-II-T2-4-COD, VOL-II-T2-4-FaecalColiforms, VOL-II-T2-4-NOTE1, VOL-II-T2-4-OilGrease, VOL-II-T2-4-ResidualChlorine, VOL-II-T2-4-TN, VOL-II-T2-4-TP, VOL-II-T2-4-TSS, VOL-II-T2-4-Turbidity, VOL-II-T2-4-pH, VOL-IV-F4C-01, VOL-IV-F4C-02, VOL-IV-F4C-03, VOL-IV-F4C-04, VOL-IV-F4C-05, VOL-IV-F4C-N1, VOL-V-29.3-01</t>
+          <t>ADD-03's cover summary does not match its provisions (C28): [not found] 'adds Volume I Clause 4.4 and a requirement for certificates of good standing': no provision of ADD-03 does this; [omitted] ADD-03/6.1 inserts new text after VOL-I:4.3; the summary does not mention it: 'The following Clause 4.4 is added to Volume I after Clause 4.3: ‘4.4 Each Bidder shall confirm in writing through the Portal, within three (3) Working Days of this Addendum, the name of its single point of contact.’'. The summary is never applied; a person decides whether to raise a clarification</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Bid manager</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>readings (automatic)</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>VOL-I-9.4-01; VOL-II-2.5-01; VOL-II-T2-4-BOD5; VOL-II-T2-4-COD; VOL-II-T2-4-FaecalColiforms; VOL-II-T2-4-NOTE1; VOL-II-T2-4-OilGrease; VOL-II-T2-4-ResidualChlorine; VOL-II-T2-4-TN; VOL-II-T2-4-TP; VOL-II-T2-4-TSS; VOL-II-T2-4-Turbidity; VOL-II-T2-4-pH; VOL-IV-F4C-01; VOL-IV-F4C-02; VOL-IV-F4C-03; VOL-IV-F4C-04; VOL-IV-F4C-05; VOL-IV-F4C-N1; VOL-V-29.3-01</t>
-        </is>
-      </c>
+          <t>C28 (automatic)</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>I-A5-lcc-ratio</t>
+          <t>I-AUTO-STALE</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>A5 lcc-ratio: INFEASIBLE by 12 WD (latest start 2026-10-06 is before the status date 2026-10-22; not compressed) (VOL-I-8.6-01; duration 5 WD is an ASSUMPTION: lcc_ratio_calc)</t>
+          <t>3 row(s) STALE at ADD-02: a dependency changed after the interpretation was made (dates recomputed; the reading needs a person). Rows: VOL-I-8.3-01, VOL-I-3.4-01, VOL-I-6.7-01</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Bid manager</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>A5 (automatic)</t>
+          <t>C11 (automatic)</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-8.6-01</t>
+          <t>VOL-I-8.3-01; VOL-I-3.4-01; VOL-I-6.7-01</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>I-A5-attendance-notice</t>
+          <t>I-AUTO-COUNTING</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>A5 attendance-notice: DEADLINE PASSED (ATTENDANCE-NOTICE = 2026-10-14 is before the status date 2026-10-22; record whether it was done) (ADD-01-3.1-01, VOL-I-5.4-01; duration 2 WD is an ASSUMPTION: clarification_drafting)</t>
+          <t>Counting conventions not stated in the pack for ATTENDANCE-NOTICE, BID-BOND-VALIDITY, PROPOSAL-VALIDITY, PROPOSAL-VALIDITY-F4A, REFERENCE-LOOKBACK: every reading is shown (A1 Dates); planning uses the conservative reading (config/assumptions.yaml)</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Bid management</t>
+          <t>Bid manager</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>A5 (automatic)</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>ADD-01-3.1-01; VOL-I-5.4-01</t>
-        </is>
-      </c>
+          <t>D4 (automatic)</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>I-A5-lcc-certificate</t>
+          <t>I-AUTO-PENDING-READINGS</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>A5 lcc-certificate: INFEASIBLE by 7 WD (latest start 2026-10-13 is before the status date 2026-10-22; not compressed) (VOL-I-8.6-01; duration 30 WD is an ASSUMPTION: lcc_certificate)</t>
+          <t>20 row(s) rely on image readings (Table 2-4, Form 4-C) still pending the owner's review. Rows: VOL-I-9.4-01, VOL-II-2.5-01, VOL-II-T2-4-BOD5, VOL-II-T2-4-COD, VOL-II-T2-4-FaecalColiforms, VOL-II-T2-4-NOTE1, VOL-II-T2-4-OilGrease, VOL-II-T2-4-ResidualChlorine, VOL-II-T2-4-TN, VOL-II-T2-4-TP, VOL-II-T2-4-TSS, VOL-II-T2-4-Turbidity, VOL-II-T2-4-pH, VOL-IV-F4C-01, VOL-IV-F4C-02, VOL-IV-F4C-03, VOL-IV-F4C-04, VOL-IV-F4C-05, VOL-IV-F4C-N1, VOL-V-29.3-01</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>A5 (automatic)</t>
+          <t>readings (automatic)</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-8.6-01</t>
+          <t>VOL-I-9.4-01; VOL-II-2.5-01; VOL-II-T2-4-BOD5; VOL-II-T2-4-COD; VOL-II-T2-4-FaecalColiforms; VOL-II-T2-4-NOTE1; VOL-II-T2-4-OilGrease; VOL-II-T2-4-ResidualChlorine; VOL-II-T2-4-TN; VOL-II-T2-4-TP; VOL-II-T2-4-TSS; VOL-II-T2-4-Turbidity; VOL-II-T2-4-pH; VOL-IV-F4C-01; VOL-IV-F4C-02; VOL-IV-F4C-03; VOL-IV-F4C-04; VOL-IV-F4C-05; VOL-IV-F4C-N1; VOL-V-29.3-01</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
+          <t>I-A5-lcc-ratio</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>A5 lcc-ratio: INFEASIBLE by 12 WD (latest start 2026-10-06 is before the status date 2026-10-22; not compressed) (VOL-I-8.6-01; duration 5 WD is an ASSUMPTION: lcc_ratio_calc)</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>A5 (automatic)</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-8.6-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>I-A5-attendance-notice</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>A5 attendance-notice: DEADLINE PASSED (ATTENDANCE-NOTICE = 2026-10-14 is before the status date 2026-10-22; record whether it was done) (ADD-01-3.1-01, VOL-I-5.4-01; duration 2 WD is an ASSUMPTION: clarification_drafting)</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Bid management</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>A5 (automatic)</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>ADD-01-3.1-01; VOL-I-5.4-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>I-A5-lcc-certificate</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>A5 lcc-certificate: INFEASIBLE by 7 WD (latest start 2026-10-13 is before the status date 2026-10-22; not compressed) (VOL-I-8.6-01; duration 30 WD is an ASSUMPTION: lcc_certificate)</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>A5 (automatic)</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-8.6-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
           <t>I-A5-FEASIBILITY</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>A5 at the status date: lcc-ratio INFEASIBLE by 12 WD; attendance-notice DEADLINE PASSED; lcc-certificate INFEASIBLE by 7 WD. Lead times are PROVISIONAL assumptions (A5 drivers)</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>Bid manager</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>A5 (automatic)</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
+      <c r="E45" s="4" t="inlineStr">
         <is>
           <t>ADD-01-3.1-01; VOL-I-5.4-01; VOL-I-8.6-01</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E42"/>
+  <autoFilter ref="A1:E45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
